--- a/Next.js/Next.xlsx
+++ b/Next.js/Next.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learner\Recap\Next.js\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A66FD14A-AB77-4F88-9098-B64E92D30120}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF786405-33F0-4CDC-A2E5-D97DAA77A53F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -194,7 +194,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -211,24 +211,6 @@
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-4.9989318521683403E-2"/>
         <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
-        <bgColor theme="9" tint="0.79998168889431442"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
-        <bgColor theme="9" tint="0.79998168889431442"/>
       </patternFill>
     </fill>
     <fill>
@@ -280,22 +262,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -604,138 +580,138 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="12" t="s">
+      <c r="C2" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="6" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="6" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" s="14" t="s">
+      <c r="C5" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="8" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="6" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" s="13" t="s">
+      <c r="A7" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="B7" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="E7" s="14" t="s">
+      <c r="C7" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="8" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="E8" s="6" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" s="9" t="s">
+      <c r="A9" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="E9" s="10" t="s">
+      <c r="D9" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" s="8" t="s">
         <v>28</v>
       </c>
     </row>
@@ -757,87 +733,87 @@
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="C11" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E11" s="6" t="s">
+      <c r="C11" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="8" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="6" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="C13" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E13" s="6" t="s">
+      <c r="C13" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E13" s="8" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="C14" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D14" s="4" t="s">
+      <c r="C14" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="6" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="E15" s="6" t="s">
+      <c r="E15" s="8" t="s">
         <v>44</v>
       </c>
     </row>
